--- a/database/event/5338/event_5338_evp_summary.xlsx
+++ b/database/event/5338/event_5338_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.8171</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8337</v>
+        <v>3.8192</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5445</v>
+        <v>3.4524</v>
       </c>
       <c r="E2" t="n">
-        <v>9.8171</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7914</v>
+        <v>4.7543</v>
       </c>
       <c r="G2" t="n">
         <v>5.0257</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2098</v>
+        <v>5.1517</v>
       </c>
       <c r="I2" t="n">
         <v>5.2829</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8404</v>
+        <v>6.7823</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6713</v>
+        <v>2.6486</v>
       </c>
       <c r="D3" t="n">
-        <v>2.342</v>
+        <v>2.2582</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8404</v>
+        <v>6.7823</v>
       </c>
       <c r="F3" t="n">
-        <v>3.139</v>
+        <v>3.0809</v>
       </c>
       <c r="G3" t="n">
         <v>3.7014</v>
       </c>
       <c r="H3" t="n">
-        <v>3.139</v>
+        <v>3.0809</v>
       </c>
       <c r="I3" t="n">
         <v>3.2127</v>
@@ -594,7 +594,7 @@
         <v>2.4817</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1459</v>
+        <v>2.0879</v>
       </c>
       <c r="E4" t="n">
         <v>6.355</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.2373</v>
+        <v>6.1624</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4358</v>
+        <v>2.4065</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0984</v>
+        <v>2.0112</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2373</v>
+        <v>6.1624</v>
       </c>
       <c r="F5" t="n">
-        <v>5.5151</v>
+        <v>5.4402</v>
       </c>
       <c r="G5" t="n">
         <v>0.7222</v>
       </c>
       <c r="H5" t="n">
-        <v>6.3447</v>
+        <v>6.2272</v>
       </c>
       <c r="I5" t="n">
         <v>6.4937</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.2044</v>
+        <v>6.1435</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4229</v>
+        <v>2.3991</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0851</v>
+        <v>2.0037</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2044</v>
+        <v>6.1435</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7555</v>
+        <v>4.6946</v>
       </c>
       <c r="G6" t="n">
         <v>1.4489</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1535</v>
+        <v>5.0581</v>
       </c>
       <c r="I6" t="n">
         <v>5.2746</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6749</v>
+        <v>5.6246</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2161</v>
+        <v>2.1965</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8712</v>
+        <v>1.7969</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6749</v>
+        <v>5.6246</v>
       </c>
       <c r="F7" t="n">
-        <v>3.391</v>
+        <v>3.3407</v>
       </c>
       <c r="G7" t="n">
         <v>2.2838</v>
       </c>
       <c r="H7" t="n">
-        <v>3.391</v>
+        <v>3.3407</v>
       </c>
       <c r="I7" t="n">
         <v>3.4546</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5386</v>
+        <v>5.4986</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1629</v>
+        <v>2.1473</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8161</v>
+        <v>1.7467</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5386</v>
+        <v>5.4986</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6935</v>
+        <v>2.6536</v>
       </c>
       <c r="G8" t="n">
         <v>2.845</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6935</v>
+        <v>2.6536</v>
       </c>
       <c r="I8" t="n">
         <v>2.744</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5229</v>
+        <v>5.4883</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1568</v>
+        <v>2.1433</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8098</v>
+        <v>1.7426</v>
       </c>
       <c r="E9" t="n">
-        <v>5.5229</v>
+        <v>5.4883</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8687</v>
+        <v>1.8341</v>
       </c>
       <c r="G9" t="n">
         <v>3.6542</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8687</v>
+        <v>1.8341</v>
       </c>
       <c r="I9" t="n">
         <v>1.9126</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.4241</v>
+        <v>5.4071</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1182</v>
+        <v>2.1116</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7699</v>
+        <v>1.7103</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4241</v>
+        <v>5.4071</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2721</v>
+        <v>2.2551</v>
       </c>
       <c r="G10" t="n">
         <v>3.152</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2721</v>
+        <v>2.2551</v>
       </c>
       <c r="I10" t="n">
         <v>2.2933</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.0781</v>
+        <v>5.0505</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9831</v>
+        <v>1.9723</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6301</v>
+        <v>1.5682</v>
       </c>
       <c r="E11" t="n">
-        <v>5.0781</v>
+        <v>5.0505</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4719</v>
+        <v>2.4444</v>
       </c>
       <c r="G11" t="n">
         <v>2.6062</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4719</v>
+        <v>2.4444</v>
       </c>
       <c r="I11" t="n">
         <v>2.5066</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.8344</v>
+        <v>4.7761</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8879</v>
+        <v>1.8651</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5316</v>
+        <v>1.4589</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8344</v>
+        <v>4.7761</v>
       </c>
       <c r="F12" t="n">
-        <v>3.9245</v>
+        <v>3.8662</v>
       </c>
       <c r="G12" t="n">
         <v>0.9099</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9245</v>
+        <v>3.8662</v>
       </c>
       <c r="I12" t="n">
         <v>3.998</v>
@@ -1008,7 +1008,7 @@
         <v>1.8185</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4599</v>
+        <v>1.4114</v>
       </c>
       <c r="E13" t="n">
         <v>4.6568</v>
@@ -1054,7 +1054,7 @@
         <v>1.7991</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4397</v>
+        <v>1.3915</v>
       </c>
       <c r="E14" t="n">
         <v>4.6069</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.5763</v>
+        <v>4.537</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7871</v>
+        <v>1.7718</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4274</v>
+        <v>1.3636</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5763</v>
+        <v>4.537</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5229</v>
+        <v>3.4836</v>
       </c>
       <c r="G15" t="n">
         <v>1.0534</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5229</v>
+        <v>3.4836</v>
       </c>
       <c r="I15" t="n">
         <v>3.5723</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.3205</v>
+        <v>4.2683</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6872</v>
+        <v>1.6668</v>
       </c>
       <c r="D16" t="n">
-        <v>1.324</v>
+        <v>1.2566</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3205</v>
+        <v>4.2683</v>
       </c>
       <c r="F16" t="n">
-        <v>4.2899</v>
+        <v>4.2377</v>
       </c>
       <c r="G16" t="n">
         <v>0.0306</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4235</v>
+        <v>4.3416</v>
       </c>
       <c r="I16" t="n">
         <v>4.5274</v>
@@ -1192,7 +1192,7 @@
         <v>1.6557</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2914</v>
+        <v>1.2452</v>
       </c>
       <c r="E17" t="n">
         <v>4.2397</v>
@@ -1238,7 +1238,7 @@
         <v>1.6376</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2727</v>
+        <v>1.2268</v>
       </c>
       <c r="E18" t="n">
         <v>4.1935</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.1227</v>
+        <v>4.0925</v>
       </c>
       <c r="C19" t="n">
-        <v>1.61</v>
+        <v>1.5982</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2441</v>
+        <v>1.1865</v>
       </c>
       <c r="E19" t="n">
-        <v>4.1227</v>
+        <v>4.0925</v>
       </c>
       <c r="F19" t="n">
-        <v>4.1774</v>
+        <v>4.1472</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0547</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2471</v>
+        <v>4.1997</v>
       </c>
       <c r="I19" t="n">
         <v>4.3067</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.9942</v>
+        <v>3.9357</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5598</v>
+        <v>1.5369</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1922</v>
+        <v>1.1241</v>
       </c>
       <c r="E20" t="n">
-        <v>3.9942</v>
+        <v>3.9357</v>
       </c>
       <c r="F20" t="n">
-        <v>4.6285</v>
+        <v>4.57</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6343</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9544</v>
+        <v>4.8626</v>
       </c>
       <c r="I20" t="n">
         <v>5.0708</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.8063</v>
+        <v>3.7932</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4864</v>
+        <v>1.4813</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1163</v>
+        <v>1.0673</v>
       </c>
       <c r="E21" t="n">
-        <v>3.8063</v>
+        <v>3.7932</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5191</v>
+        <v>3.506</v>
       </c>
       <c r="G21" t="n">
         <v>0.2872</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5191</v>
+        <v>3.506</v>
       </c>
       <c r="I21" t="n">
         <v>3.5355</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.7624</v>
+        <v>3.7393</v>
       </c>
       <c r="C22" t="n">
-        <v>1.4693</v>
+        <v>1.4603</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0986</v>
+        <v>1.0458</v>
       </c>
       <c r="E22" t="n">
-        <v>3.7624</v>
+        <v>3.7393</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5565</v>
+        <v>1.5334</v>
       </c>
       <c r="G22" t="n">
         <v>2.2059</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5565</v>
+        <v>1.5334</v>
       </c>
       <c r="I22" t="n">
         <v>1.5856</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.566</v>
+        <v>3.5422</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3926</v>
+        <v>1.3833</v>
       </c>
       <c r="D23" t="n">
-        <v>1.0192</v>
+        <v>0.9673</v>
       </c>
       <c r="E23" t="n">
-        <v>3.566</v>
+        <v>3.5422</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4215</v>
+        <v>3.3821</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8555</v>
+        <v>0.1601</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6298</v>
+        <v>3.3821</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7386</v>
+        <v>2.7413</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8555</v>
+        <v>0.1601</v>
       </c>
       <c r="K23" t="n">
-        <v>365</v>
+        <v>203</v>
       </c>
       <c r="L23" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8831</v>
+        <v>2.9014</v>
       </c>
       <c r="N23" t="n">
-        <v>527</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24">
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.5506</v>
+        <v>3.5127</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3866</v>
+        <v>1.3718</v>
       </c>
       <c r="D24" t="n">
-        <v>1.013</v>
+        <v>0.9555</v>
       </c>
       <c r="E24" t="n">
-        <v>3.5506</v>
+        <v>3.5127</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0458</v>
+        <v>2.0079</v>
       </c>
       <c r="G24" t="n">
         <v>1.5048</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0458</v>
+        <v>2.0079</v>
       </c>
       <c r="I24" t="n">
         <v>2.0939</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.5422</v>
+        <v>3.5113</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3833</v>
+        <v>1.3712</v>
       </c>
       <c r="D25" t="n">
-        <v>1.0096</v>
+        <v>0.955</v>
       </c>
       <c r="E25" t="n">
-        <v>3.5422</v>
+        <v>3.5113</v>
       </c>
       <c r="F25" t="n">
-        <v>3.3821</v>
+        <v>4.3668</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1601</v>
+        <v>-0.8555</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3821</v>
+        <v>4.5441</v>
       </c>
       <c r="I25" t="n">
-        <v>2.7413</v>
+        <v>4.7386</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1601</v>
+        <v>-0.8555</v>
       </c>
       <c r="K25" t="n">
-        <v>203</v>
+        <v>365</v>
       </c>
       <c r="L25" t="n">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9014</v>
+        <v>3.8831</v>
       </c>
       <c r="N25" t="n">
-        <v>275</v>
+        <v>527</v>
       </c>
     </row>
     <row r="26">
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.3984</v>
+        <v>3.3674</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3271</v>
+        <v>1.315</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9515</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>3.3984</v>
+        <v>3.3674</v>
       </c>
       <c r="F26" t="n">
-        <v>2.7803</v>
+        <v>2.7493</v>
       </c>
       <c r="G26" t="n">
         <v>0.6181</v>
       </c>
       <c r="H26" t="n">
-        <v>2.7803</v>
+        <v>2.7493</v>
       </c>
       <c r="I26" t="n">
         <v>2.8193</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.3363</v>
+        <v>3.2876</v>
       </c>
       <c r="C27" t="n">
-        <v>1.3029</v>
+        <v>1.2839</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9264</v>
+        <v>0.8659</v>
       </c>
       <c r="E27" t="n">
-        <v>3.3363</v>
+        <v>3.2876</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2838</v>
+        <v>3.2351</v>
       </c>
       <c r="G27" t="n">
         <v>0.0525</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2838</v>
+        <v>3.2351</v>
       </c>
       <c r="I27" t="n">
         <v>3.3454</v>
@@ -1698,7 +1698,7 @@
         <v>1.2801</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9029</v>
+        <v>0.862</v>
       </c>
       <c r="E28" t="n">
         <v>3.278</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.9724</v>
+        <v>2.932</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1608</v>
+        <v>1.145</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7794</v>
+        <v>0.7242</v>
       </c>
       <c r="E29" t="n">
-        <v>2.9724</v>
+        <v>2.932</v>
       </c>
       <c r="F29" t="n">
-        <v>2.6851</v>
+        <v>1.4515</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2873</v>
+        <v>1.4805</v>
       </c>
       <c r="H29" t="n">
-        <v>2.6851</v>
+        <v>1.4515</v>
       </c>
       <c r="I29" t="n">
-        <v>2.7481</v>
+        <v>1.4885</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2873</v>
+        <v>1.4805</v>
       </c>
       <c r="K29" t="n">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="L29" t="n">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="M29" t="n">
-        <v>3.0354</v>
+        <v>2.969</v>
       </c>
       <c r="N29" t="n">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.9484</v>
+        <v>2.9227</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1514</v>
+        <v>1.1414</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.7205</v>
       </c>
       <c r="E30" t="n">
-        <v>2.9484</v>
+        <v>2.9227</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4679</v>
+        <v>2.6354</v>
       </c>
       <c r="G30" t="n">
-        <v>1.4805</v>
+        <v>0.2873</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4679</v>
+        <v>2.6354</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4885</v>
+        <v>2.7481</v>
       </c>
       <c r="J30" t="n">
-        <v>1.4805</v>
+        <v>0.2873</v>
       </c>
       <c r="K30" t="n">
-        <v>175</v>
+        <v>276</v>
       </c>
       <c r="L30" t="n">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="M30" t="n">
-        <v>2.969</v>
+        <v>3.0354</v>
       </c>
       <c r="N30" t="n">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31">
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.6656</v>
+        <v>2.6508</v>
       </c>
       <c r="C31" t="n">
-        <v>1.041</v>
+        <v>1.0352</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6555</v>
+        <v>0.6122</v>
       </c>
       <c r="E31" t="n">
-        <v>2.6656</v>
+        <v>2.6508</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8</v>
+        <v>0.7852</v>
       </c>
       <c r="G31" t="n">
         <v>1.8656</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8</v>
+        <v>0.7852</v>
       </c>
       <c r="I31" t="n">
         <v>0.8188</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.4999</v>
+        <v>2.4787</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9762</v>
+        <v>0.968</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5885</v>
+        <v>0.5436</v>
       </c>
       <c r="E32" t="n">
-        <v>2.4999</v>
+        <v>2.4787</v>
       </c>
       <c r="F32" t="n">
-        <v>2.8449</v>
+        <v>2.8237</v>
       </c>
       <c r="G32" t="n">
         <v>-0.345</v>
       </c>
       <c r="H32" t="n">
-        <v>2.8449</v>
+        <v>2.8237</v>
       </c>
       <c r="I32" t="n">
         <v>2.8714</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.4838</v>
+        <v>2.4377</v>
       </c>
       <c r="C33" t="n">
-        <v>0.97</v>
+        <v>0.952</v>
       </c>
       <c r="D33" t="n">
-        <v>0.582</v>
+        <v>0.5273</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4838</v>
+        <v>2.4377</v>
       </c>
       <c r="F33" t="n">
-        <v>2.4877</v>
+        <v>2.4416</v>
       </c>
       <c r="G33" t="n">
         <v>-0.0039</v>
       </c>
       <c r="H33" t="n">
-        <v>2.4877</v>
+        <v>2.4416</v>
       </c>
       <c r="I33" t="n">
         <v>2.5461</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.3026</v>
+        <v>2.2855</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8992</v>
+        <v>0.8925</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5088</v>
+        <v>0.4666</v>
       </c>
       <c r="E34" t="n">
-        <v>2.3026</v>
+        <v>2.2855</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9228</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>1.3798</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9228</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="I34" t="n">
         <v>0.9445</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.2258</v>
+        <v>2.2073</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8692</v>
+        <v>0.862</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4778</v>
+        <v>0.4355</v>
       </c>
       <c r="E35" t="n">
-        <v>2.2258</v>
+        <v>2.2073</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6585</v>
+        <v>1.64</v>
       </c>
       <c r="G35" t="n">
         <v>0.5673</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6585</v>
+        <v>1.64</v>
       </c>
       <c r="I35" t="n">
         <v>1.6818</v>
@@ -2066,7 +2066,7 @@
         <v>0.8267</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4338</v>
+        <v>0.3995</v>
       </c>
       <c r="E36" t="n">
         <v>2.1169</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.0826</v>
+        <v>2.0745</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8133</v>
+        <v>0.8101</v>
       </c>
       <c r="D37" t="n">
-        <v>0.42</v>
+        <v>0.3826</v>
       </c>
       <c r="E37" t="n">
-        <v>2.0826</v>
+        <v>2.0745</v>
       </c>
       <c r="F37" t="n">
-        <v>2.1678</v>
+        <v>2.1597</v>
       </c>
       <c r="G37" t="n">
         <v>-0.0852</v>
       </c>
       <c r="H37" t="n">
-        <v>2.1678</v>
+        <v>2.1597</v>
       </c>
       <c r="I37" t="n">
         <v>2.1779</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.8969</v>
+        <v>1.8941</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7408</v>
+        <v>0.7397</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3449</v>
+        <v>0.3107</v>
       </c>
       <c r="E38" t="n">
-        <v>1.8969</v>
+        <v>1.8941</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3686</v>
+        <v>0.3658</v>
       </c>
       <c r="G38" t="n">
         <v>1.5283</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3686</v>
+        <v>0.3658</v>
       </c>
       <c r="I38" t="n">
         <v>0.372</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.753</v>
+        <v>1.7246</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6846</v>
+        <v>0.6735</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2868</v>
+        <v>0.2432</v>
       </c>
       <c r="E39" t="n">
-        <v>1.753</v>
+        <v>1.7246</v>
       </c>
       <c r="F39" t="n">
-        <v>1.5344</v>
+        <v>1.506</v>
       </c>
       <c r="G39" t="n">
         <v>0.2186</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5344</v>
+        <v>1.506</v>
       </c>
       <c r="I39" t="n">
         <v>1.5705</v>
@@ -2250,7 +2250,7 @@
         <v>0.6002999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1996</v>
+        <v>0.1685</v>
       </c>
       <c r="E40" t="n">
         <v>1.5371</v>
@@ -2296,7 +2296,7 @@
         <v>0.5392</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1364</v>
+        <v>0.1062</v>
       </c>
       <c r="E41" t="n">
         <v>1.3807</v>
@@ -2342,7 +2342,7 @@
         <v>0.5292</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1261</v>
+        <v>0.096</v>
       </c>
       <c r="E42" t="n">
         <v>1.3552</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.2774</v>
+        <v>1.272</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4988</v>
+        <v>0.4967</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0629</v>
       </c>
       <c r="E43" t="n">
-        <v>1.2774</v>
+        <v>1.272</v>
       </c>
       <c r="F43" t="n">
-        <v>1.4645</v>
+        <v>1.4591</v>
       </c>
       <c r="G43" t="n">
         <v>-0.1871</v>
       </c>
       <c r="H43" t="n">
-        <v>1.4645</v>
+        <v>1.4591</v>
       </c>
       <c r="I43" t="n">
         <v>1.4713</v>
@@ -2434,7 +2434,7 @@
         <v>0.4792</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0743</v>
+        <v>0.0449</v>
       </c>
       <c r="E44" t="n">
         <v>1.227</v>
@@ -2480,7 +2480,7 @@
         <v>0.4568</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0512</v>
+        <v>0.0221</v>
       </c>
       <c r="E45" t="n">
         <v>1.1697</v>
@@ -2526,7 +2526,7 @@
         <v>0.2838</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1278</v>
+        <v>-0.1544</v>
       </c>
       <c r="E46" t="n">
         <v>0.7267</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7063</v>
+        <v>0.697</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2758</v>
+        <v>0.2722</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.136</v>
+        <v>-0.1662</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7063</v>
+        <v>0.697</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.8249</v>
       </c>
       <c r="G47" t="n">
         <v>-0.1279</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.8249</v>
       </c>
       <c r="I47" t="n">
         <v>0.8459</v>
@@ -2618,7 +2618,7 @@
         <v>0.1371</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2796</v>
+        <v>-0.3041</v>
       </c>
       <c r="E48" t="n">
         <v>0.351</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1906</v>
+        <v>0.1821</v>
       </c>
       <c r="C49" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0711</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3444</v>
+        <v>-0.3714</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1906</v>
+        <v>0.1821</v>
       </c>
       <c r="F49" t="n">
-        <v>1.141</v>
+        <v>1.1325</v>
       </c>
       <c r="G49" t="n">
         <v>-0.9504</v>
       </c>
       <c r="H49" t="n">
-        <v>1.141</v>
+        <v>1.1325</v>
       </c>
       <c r="I49" t="n">
         <v>1.1516</v>
@@ -2710,7 +2710,7 @@
         <v>0.0294</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.391</v>
+        <v>-0.414</v>
       </c>
       <c r="E50" t="n">
         <v>0.0752</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0944</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.519</v>
+        <v>-0.5402</v>
       </c>
       <c r="E51" t="n">
         <v>-0.2417</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1093</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5345</v>
+        <v>-0.5555</v>
       </c>
       <c r="E52" t="n">
         <v>-0.28</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1445</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5709</v>
+        <v>-0.5914</v>
       </c>
       <c r="E53" t="n">
         <v>-0.3701</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1554</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5821</v>
+        <v>-0.6024</v>
       </c>
       <c r="E54" t="n">
         <v>-0.3979</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1702</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5975</v>
+        <v>-0.6176</v>
       </c>
       <c r="E55" t="n">
         <v>-0.4359</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2067</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6352</v>
+        <v>-0.6548</v>
       </c>
       <c r="E56" t="n">
         <v>-0.5294</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2157</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6445</v>
+        <v>-0.664</v>
       </c>
       <c r="E57" t="n">
         <v>-0.5524</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5774</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2255</v>
+        <v>-0.2242</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6546</v>
+        <v>-0.6726</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5774</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.9004</v>
+        <v>-0.8971</v>
       </c>
       <c r="G58" t="n">
         <v>0.323</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.9004</v>
+        <v>-0.8971</v>
       </c>
       <c r="I58" t="n">
         <v>-0.9046</v>
@@ -3124,7 +3124,7 @@
         <v>-0.273</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7037</v>
+        <v>-0.7224</v>
       </c>
       <c r="E59" t="n">
         <v>-0.699</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2916</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.723</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="E60" t="n">
         <v>-0.7466</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3248</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7573</v>
+        <v>-0.7752</v>
       </c>
       <c r="E61" t="n">
         <v>-0.8316</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3513</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7847</v>
+        <v>-0.8023</v>
       </c>
       <c r="E62" t="n">
         <v>-0.8995</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.9489</v>
+        <v>-0.9479</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3706</v>
+        <v>-0.3702</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8047</v>
+        <v>-0.8216</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.9489</v>
+        <v>-0.9479</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0961</v>
       </c>
       <c r="G63" t="n">
         <v>-0.8518</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0961</v>
       </c>
       <c r="I63" t="n">
         <v>-0.0985</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3737</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8079</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9569</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3841</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8187</v>
+        <v>-0.8357</v>
       </c>
       <c r="E65" t="n">
         <v>-0.9835</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.039</v>
+        <v>-1.0362</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4057</v>
+        <v>-0.4047</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8411</v>
+        <v>-0.8567</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.039</v>
+        <v>-1.0362</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7518</v>
+        <v>-0.749</v>
       </c>
       <c r="G66" t="n">
         <v>-0.2872</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7518</v>
+        <v>-0.749</v>
       </c>
       <c r="I66" t="n">
         <v>-0.7553</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4121</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8477</v>
+        <v>-0.8643</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0553</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4324</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8687</v>
+        <v>-0.8851</v>
       </c>
       <c r="E68" t="n">
         <v>-1.1073</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4339</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8702</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1111</v>
@@ -3630,7 +3630,7 @@
         <v>-0.4883</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9265</v>
+        <v>-0.9421</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2505</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5462</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-1.0012</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3987</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6042999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0465</v>
+        <v>-1.0604</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5474</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.6235</v>
+        <v>-1.5976</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.634</v>
+        <v>-0.6239</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0772</v>
+        <v>-1.0804</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.6235</v>
+        <v>-1.5976</v>
       </c>
       <c r="F73" t="n">
-        <v>-2.3289</v>
+        <v>-2.303</v>
       </c>
       <c r="G73" t="n">
         <v>0.7054</v>
       </c>
       <c r="H73" t="n">
-        <v>-2.3289</v>
+        <v>-2.303</v>
       </c>
       <c r="I73" t="n">
         <v>-2.3616</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7157</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1618</v>
+        <v>-1.1741</v>
       </c>
       <c r="E74" t="n">
         <v>-1.8328</v>
@@ -3860,7 +3860,7 @@
         <v>-0.726</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1724</v>
+        <v>-1.1846</v>
       </c>
       <c r="E75" t="n">
         <v>-1.8591</v>
@@ -3906,7 +3906,7 @@
         <v>-0.7276</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.174</v>
+        <v>-1.1862</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8631</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7317</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1783</v>
+        <v>-1.1904</v>
       </c>
       <c r="E77" t="n">
         <v>-1.8738</v>
@@ -3998,7 +3998,7 @@
         <v>-0.8207</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2703</v>
+        <v>-1.2811</v>
       </c>
       <c r="E78" t="n">
         <v>-2.1015</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.7884</v>
+        <v>-2.7525</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.0889</v>
+        <v>-1.0749</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5478</v>
+        <v>-1.5405</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.7884</v>
+        <v>-2.7525</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.9372</v>
+        <v>-1.9013</v>
       </c>
       <c r="G79" t="n">
         <v>-0.8512</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.9372</v>
+        <v>-1.9013</v>
       </c>
       <c r="I79" t="n">
         <v>-1.9827</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.2528</v>
+        <v>-3.238</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.2703</v>
+        <v>-1.2645</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7354</v>
+        <v>-1.7339</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.2528</v>
+        <v>-3.238</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.9837</v>
+        <v>-1.9689</v>
       </c>
       <c r="G80" t="n">
         <v>-1.2691</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.9837</v>
+        <v>-1.9689</v>
       </c>
       <c r="I80" t="n">
         <v>-2.0022</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.6092</v>
+        <v>-4.5609</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.8</v>
+        <v>-1.7811</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2834</v>
+        <v>-2.261</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.6092</v>
+        <v>-4.5609</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.6092</v>
+        <v>-2.5609</v>
       </c>
       <c r="G81" t="n">
         <v>-2</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.6092</v>
+        <v>-2.5609</v>
       </c>
       <c r="I81" t="n">
         <v>-2.6705</v>
